--- a/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
+++ b/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
@@ -1802,7 +1802,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="795">
+  <cellXfs count="797">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3504,6 +3504,8 @@
     <xf numFmtId="177" fontId="15" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="9" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5148,7 +5150,9 @@
 IF (Platinum Agent, cashback = (0.001 * Nxxx capped at N20.00)</t>
         </is>
       </c>
-      <c r="H14" s="368" t="n"/>
+      <c r="H14" s="795" t="n">
+        <v>0</v>
+      </c>
       <c r="J14" s="728" t="n"/>
     </row>
     <row r="15" ht="41" customHeight="1" s="581" thickBot="1">
@@ -5174,15 +5178,19 @@
       </c>
       <c r="F15" s="729" t="inlineStr">
         <is>
-          <t>Part Fees to Elkanah Suspense (= ISW + Revenue to 9PSB + VAT on revenue).
-IF (Silver Agent = 0.00460 * Nxxx, capped at N75.00)
-IF (Gold Agent = 0.00410 * Nxxx, capped at N65.00)
-IF (Platinum Agent = 0.00360 * Nxxx, capped at N55.00)
-Derivation / breakdown of Part Fees (the portion 9PSB keeps = Revenue + VAT; the ISW fee is settled on the Core Banking System and therefore does NOT reflect as 9PSB income here):
-  - ISW (settled on Core Banking): 0.003225 * Nxxx (capped at N21.50)
-  - Revenue to 9PSB: Silver 0.00127907 (cap N65.58) | Gold 0.000813953 (cap N56.28) | Platinum 0.000348837 (cap N46.98)
-  - VAT on revenue: Silver 0.0000959302 (cap N4.92) | Gold 0.0000610465 (cap N4.22) | Platinum 0.0000261628 (cap N3.52)</t>
-        </is>
+          <t>Part Fees to Elkanah Suspense = Total Charge - SLP - Cashback  (the residual).
+= ISW + Revenue to 9PSB + VAT on revenue.
+  Uncapped portion: Silver 0.0046 x Nxxx | Gold 0.0041 x Nxxx | Platinum 0.0036 x Nxxx.
+  Effective ceiling at large amounts (Total, SLP &amp; ISW each capped): Silver N75.00 | Gold N65.00 | Platinum N55.00.
+9PSB keeps Revenue + VAT; the ISW fee is settled on the Core Banking System and does NOT reflect as 9PSB income here:
+  - ISW (settled on Core Banking): 0.003225 x Nxxx (capped at N21.50)
+  - Revenue to 9PSB = (Part Fees - ISW) x 100/107.5
+  - VAT on revenue  = 7.5% x Revenue</t>
+        </is>
+      </c>
+      <c r="H15" s="796">
+        <f>-H12-H13-H14</f>
+        <v/>
       </c>
       <c r="I15" s="730" t="n"/>
     </row>
@@ -6003,7 +6011,9 @@
 IF (Platinum Agent, cashback = (0.001 * Nxxx capped at N20.00)</t>
         </is>
       </c>
-      <c r="H16" s="368" t="n"/>
+      <c r="H16" s="795" t="n">
+        <v>0</v>
+      </c>
       <c r="J16" s="728" t="n"/>
     </row>
     <row r="17" ht="41" customHeight="1" s="581" thickBot="1">
@@ -6029,15 +6039,19 @@
       </c>
       <c r="F17" s="729" t="inlineStr">
         <is>
-          <t>Part Fees to Elkanah Suspense (= ISW + Revenue to 9PSB + VAT on revenue).
-IF (Silver Agent = 0.00460 * Nxxx, capped at N75.00)
-IF (Gold Agent = 0.00410 * Nxxx, capped at N65.00)
-IF (Platinum Agent = 0.00360 * Nxxx, capped at N55.00)
-Derivation / breakdown of Part Fees (the portion 9PSB keeps = Revenue + VAT; the ISW fee is settled on the Core Banking System and therefore does NOT reflect as 9PSB income here):
-  - ISW (settled on Core Banking): 0.003225 * Nxxx (capped at N21.50)
-  - Revenue to 9PSB: Silver 0.00127907 (cap N65.58) | Gold 0.000813953 (cap N56.28) | Platinum 0.000348837 (cap N46.98)
-  - VAT on revenue: Silver 0.0000959302 (cap N4.92) | Gold 0.0000610465 (cap N4.22) | Platinum 0.0000261628 (cap N3.52)</t>
-        </is>
+          <t>Part Fees to Elkanah Suspense = Total Charge - SLP - Cashback  (the residual).
+= ISW + Revenue to 9PSB + VAT on revenue.
+  Uncapped portion: Silver 0.0046 x Nxxx | Gold 0.0041 x Nxxx | Platinum 0.0036 x Nxxx.
+  Effective ceiling at large amounts (Total, SLP &amp; ISW each capped): Silver N75.00 | Gold N65.00 | Platinum N55.00.
+9PSB keeps Revenue + VAT; the ISW fee is settled on the Core Banking System and does NOT reflect as 9PSB income here:
+  - ISW (settled on Core Banking): 0.003225 x Nxxx (capped at N21.50)
+  - Revenue to 9PSB = (Part Fees - ISW) x 100/107.5
+  - VAT on revenue  = 7.5% x Revenue</t>
+        </is>
+      </c>
+      <c r="H17" s="796">
+        <f>-H14-H15-H16</f>
+        <v/>
       </c>
       <c r="I17" s="730" t="n"/>
     </row>

--- a/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
+++ b/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
@@ -5369,13 +5369,13 @@
       </c>
       <c r="F26" s="490" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.00127907 * Nxxx capped at N65.58), 
-IF (Gold Agent = 0.000813953 * Nxxx capped at N56.28), 
-IF (Platinum Agent = 0.000348837 * Nxxx capped at N46.98)</t>
+          <t>IF (Silver Agent = 0.00127907 * Nxxx capped at N49.77), 
+IF (Gold Agent = 0.000813953 * Nxxx capped at N40.47), 
+IF (Platinum Agent = 0.000348837 * Nxxx capped at N31.16)</t>
         </is>
       </c>
       <c r="H26" s="491">
-        <f>IF(0.00127907*H19&gt;65.58,65.58,0.00127907*H19)</f>
+        <f>IF(0.00127907*H19&gt;49.77,49.77,0.00127907*H19)</f>
         <v/>
       </c>
       <c r="J26" s="281">
@@ -5404,13 +5404,13 @@
       </c>
       <c r="F27" s="490" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.0000959302 * Nxxx capped at N4.92 ), 
-IF (Gold Agent = 0.0000610465 * Nxxx capped at N4.22 ), 
-IF (Platinum Agent = 0.0000261628 * Nxxx capped at N3.52)</t>
+          <t>IF (Silver Agent = 0.0000959302 * Nxxx capped at N3.73 ), 
+IF (Gold Agent = 0.0000610465 * Nxxx capped at N3.03 ), 
+IF (Platinum Agent = 0.0000261628 * Nxxx capped at N2.34)</t>
         </is>
       </c>
       <c r="H27" s="491">
-        <f>IF(0.0000959302*H19&gt;4.92,4.92,0.0000959302*H19)</f>
+        <f>IF(0.0000959302*H19&gt;3.73,3.73,0.0000959302*H19)</f>
         <v/>
       </c>
       <c r="J27" s="281">
@@ -6230,13 +6230,13 @@
       </c>
       <c r="F28" s="490" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.00127907 * Nxxx capped at N65.58), 
-IF (Gold Agent = 0.000813953 * Nxxx capped at N56.28), 
-IF (Platinum Agent = 0.000348837 * Nxxx capped at N46.98)</t>
+          <t>IF (Silver Agent = 0.00127907 * Nxxx capped at N49.77), 
+IF (Gold Agent = 0.000813953 * Nxxx capped at N40.47), 
+IF (Platinum Agent = 0.000348837 * Nxxx capped at N31.16)</t>
         </is>
       </c>
       <c r="H28" s="491">
-        <f>IF(0.00127907*H21&gt;65.58,65.58,0.00127907*H21)</f>
+        <f>IF(0.00127907*H21&gt;49.77,49.77,0.00127907*H21)</f>
         <v/>
       </c>
       <c r="J28" s="281">
@@ -6265,13 +6265,13 @@
       </c>
       <c r="F29" s="490" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.0000959302 * Nxxx capped at N4.92 ), 
-IF (Gold Agent = 0.0000610465 * Nxxx capped at N4.22 ), 
-IF (Platinum Agent = 0.0000261628 * Nxxx capped at N3.52)</t>
+          <t>IF (Silver Agent = 0.0000959302 * Nxxx capped at N3.73 ), 
+IF (Gold Agent = 0.0000610465 * Nxxx capped at N3.03 ), 
+IF (Platinum Agent = 0.0000261628 * Nxxx capped at N2.34)</t>
         </is>
       </c>
       <c r="H29" s="491">
-        <f>IF(0.0000959302*H21&gt;4.92,4.92,0.0000959302*H21)</f>
+        <f>IF(0.0000959302*H21&gt;3.73,3.73,0.0000959302*H21)</f>
         <v/>
       </c>
     </row>

--- a/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
+++ b/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
@@ -5178,14 +5178,10 @@
       </c>
       <c r="F15" s="729" t="inlineStr">
         <is>
-          <t>Part Fees to Elkanah Suspense = Total Charge - SLP - Cashback  (the residual).
-= ISW + Revenue to 9PSB + VAT on revenue.
-  Uncapped portion: Silver 0.0046 x Nxxx | Gold 0.0041 x Nxxx | Platinum 0.0036 x Nxxx.
-  Effective ceiling at large amounts (Total, SLP &amp; ISW each capped): Silver N75.00 | Gold N65.00 | Platinum N55.00.
-9PSB keeps Revenue + VAT; the ISW fee is settled on the Core Banking System and does NOT reflect as 9PSB income here:
-  - ISW (settled on Core Banking): 0.003225 x Nxxx (capped at N21.50)
-  - Revenue to 9PSB = (Part Fees - ISW) x 100/107.5
-  - VAT on revenue  = 7.5% x Revenue</t>
+          <t>Part Fees to Elkanah Suspense = Total Charge - SLP - Cashback (residual) -&gt; settled on Core Banking as ISW + Revenue to 9PSB + VAT.
+Silver 0.46% | Gold 0.41% | Platinum 0.36% of Nxxx (up to the N100 total-charge cap).
+Maximum Part Fees (at N20,000, where the N100 total cap binds): Silver N92.00 | Gold N82.00 | Platinum N72.00
+  = ISW N21.50 + Revenue (Silver 65.58 / Gold 56.28 / Platinum 46.98) + VAT (Silver 4.92 / Gold 4.22 / Platinum 3.52).</t>
         </is>
       </c>
       <c r="H15" s="796">
@@ -5369,13 +5365,13 @@
       </c>
       <c r="F26" s="490" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.00127907 * Nxxx capped at N49.77), 
-IF (Gold Agent = 0.000813953 * Nxxx capped at N40.47), 
-IF (Platinum Agent = 0.000348837 * Nxxx capped at N31.16)</t>
+          <t>IF (Silver Agent = 0.00127907 * Nxxx capped at N65.58), 
+IF (Gold Agent = 0.000813953 * Nxxx capped at N56.28), 
+IF (Platinum Agent = 0.000348837 * Nxxx capped at N46.98)</t>
         </is>
       </c>
       <c r="H26" s="491">
-        <f>IF(0.00127907*H19&gt;49.77,49.77,0.00127907*H19)</f>
+        <f>IF(0.00127907*H19&gt;65.58,65.58,0.00127907*H19)</f>
         <v/>
       </c>
       <c r="J26" s="281">
@@ -5404,13 +5400,13 @@
       </c>
       <c r="F27" s="490" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.0000959302 * Nxxx capped at N3.73 ), 
-IF (Gold Agent = 0.0000610465 * Nxxx capped at N3.03 ), 
-IF (Platinum Agent = 0.0000261628 * Nxxx capped at N2.34)</t>
+          <t>IF (Silver Agent = 0.0000959302 * Nxxx capped at N4.92 ), 
+IF (Gold Agent = 0.0000610465 * Nxxx capped at N4.22 ), 
+IF (Platinum Agent = 0.0000261628 * Nxxx capped at N3.52)</t>
         </is>
       </c>
       <c r="H27" s="491">
-        <f>IF(0.0000959302*H19&gt;3.73,3.73,0.0000959302*H19)</f>
+        <f>IF(0.0000959302*H19&gt;4.92,4.92,0.0000959302*H19)</f>
         <v/>
       </c>
       <c r="J27" s="281">
@@ -6039,14 +6035,10 @@
       </c>
       <c r="F17" s="729" t="inlineStr">
         <is>
-          <t>Part Fees to Elkanah Suspense = Total Charge - SLP - Cashback  (the residual).
-= ISW + Revenue to 9PSB + VAT on revenue.
-  Uncapped portion: Silver 0.0046 x Nxxx | Gold 0.0041 x Nxxx | Platinum 0.0036 x Nxxx.
-  Effective ceiling at large amounts (Total, SLP &amp; ISW each capped): Silver N75.00 | Gold N65.00 | Platinum N55.00.
-9PSB keeps Revenue + VAT; the ISW fee is settled on the Core Banking System and does NOT reflect as 9PSB income here:
-  - ISW (settled on Core Banking): 0.003225 x Nxxx (capped at N21.50)
-  - Revenue to 9PSB = (Part Fees - ISW) x 100/107.5
-  - VAT on revenue  = 7.5% x Revenue</t>
+          <t>Part Fees to Elkanah Suspense = Total Charge - SLP - Cashback (residual) -&gt; settled on Core Banking as ISW + Revenue to 9PSB + VAT.
+Silver 0.46% | Gold 0.41% | Platinum 0.36% of Nxxx (up to the N100 total-charge cap).
+Maximum Part Fees (at N20,000, where the N100 total cap binds): Silver N92.00 | Gold N82.00 | Platinum N72.00
+  = ISW N21.50 + Revenue (Silver 65.58 / Gold 56.28 / Platinum 46.98) + VAT (Silver 4.92 / Gold 4.22 / Platinum 3.52).</t>
         </is>
       </c>
       <c r="H17" s="796">
@@ -6230,13 +6222,13 @@
       </c>
       <c r="F28" s="490" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.00127907 * Nxxx capped at N49.77), 
-IF (Gold Agent = 0.000813953 * Nxxx capped at N40.47), 
-IF (Platinum Agent = 0.000348837 * Nxxx capped at N31.16)</t>
+          <t>IF (Silver Agent = 0.00127907 * Nxxx capped at N65.58), 
+IF (Gold Agent = 0.000813953 * Nxxx capped at N56.28), 
+IF (Platinum Agent = 0.000348837 * Nxxx capped at N46.98)</t>
         </is>
       </c>
       <c r="H28" s="491">
-        <f>IF(0.00127907*H21&gt;49.77,49.77,0.00127907*H21)</f>
+        <f>IF(0.00127907*H21&gt;65.58,65.58,0.00127907*H21)</f>
         <v/>
       </c>
       <c r="J28" s="281">
@@ -6265,13 +6257,13 @@
       </c>
       <c r="F29" s="490" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.0000959302 * Nxxx capped at N3.73 ), 
-IF (Gold Agent = 0.0000610465 * Nxxx capped at N3.03 ), 
-IF (Platinum Agent = 0.0000261628 * Nxxx capped at N2.34)</t>
+          <t>IF (Silver Agent = 0.0000959302 * Nxxx capped at N4.92 ), 
+IF (Gold Agent = 0.0000610465 * Nxxx capped at N4.22 ), 
+IF (Platinum Agent = 0.0000261628 * Nxxx capped at N3.52)</t>
         </is>
       </c>
       <c r="H29" s="491">
-        <f>IF(0.0000959302*H21&gt;3.73,3.73,0.0000959302*H21)</f>
+        <f>IF(0.0000959302*H21&gt;4.92,4.92,0.0000959302*H21)</f>
         <v/>
       </c>
     </row>

--- a/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
+++ b/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
@@ -5178,10 +5178,9 @@
       </c>
       <c r="F15" s="729" t="inlineStr">
         <is>
-          <t>Part Fees to Elkanah Suspense = Total Charge - SLP - Cashback (residual) -&gt; settled on Core Banking as ISW + Revenue to 9PSB + VAT.
-Silver 0.46% | Gold 0.41% | Platinum 0.36% of Nxxx (up to the N100 total-charge cap).
-Maximum Part Fees (at N20,000, where the N100 total cap binds): Silver N92.00 | Gold N82.00 | Platinum N72.00
-  = ISW N21.50 + Revenue (Silver 65.58 / Gold 56.28 / Platinum 46.98) + VAT (Silver 4.92 / Gold 4.22 / Platinum 3.52).</t>
+          <t>IF (Silver Agent = 0.0046 * Nxxx capped at N92.00), 
+IF (Gold Agent = 0.0041 * Nxxx capped at N82.00), 
+IF (Platinum Agent = 0.0036 * Nxxx capped at N72.00)</t>
         </is>
       </c>
       <c r="H15" s="796">
@@ -6035,10 +6034,9 @@
       </c>
       <c r="F17" s="729" t="inlineStr">
         <is>
-          <t>Part Fees to Elkanah Suspense = Total Charge - SLP - Cashback (residual) -&gt; settled on Core Banking as ISW + Revenue to 9PSB + VAT.
-Silver 0.46% | Gold 0.41% | Platinum 0.36% of Nxxx (up to the N100 total-charge cap).
-Maximum Part Fees (at N20,000, where the N100 total cap binds): Silver N92.00 | Gold N82.00 | Platinum N72.00
-  = ISW N21.50 + Revenue (Silver 65.58 / Gold 56.28 / Platinum 46.98) + VAT (Silver 4.92 / Gold 4.22 / Platinum 3.52).</t>
+          <t>IF (Silver Agent = 0.0046 * Nxxx capped at N92.00), 
+IF (Gold Agent = 0.0041 * Nxxx capped at N82.00), 
+IF (Platinum Agent = 0.0036 * Nxxx capped at N72.00)</t>
         </is>
       </c>
       <c r="H17" s="796">

--- a/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
+++ b/Updated_Agent_User_Accounting_Schematics_EMTL_ISW_VATincl (updated).xlsx
@@ -1802,7 +1802,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="797">
+  <cellXfs count="799">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3506,6 +3506,8 @@
     </xf>
     <xf numFmtId="2" fontId="9" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="2" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5173,32 +5175,61 @@
       </c>
       <c r="E15" s="102" t="inlineStr">
         <is>
-          <t>Part Fees</t>
+          <t>ISW Fee (pass-through; settled at switch on Core Banking)</t>
         </is>
       </c>
       <c r="F15" s="729" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.0046 * Nxxx capped at N92.00), 
-IF (Gold Agent = 0.0041 * Nxxx capped at N82.00), 
-IF (Platinum Agent = 0.0036 * Nxxx capped at N72.00)</t>
+          <t>0.003225 * Nxxx (capped at N21.50)</t>
         </is>
       </c>
       <c r="H15" s="796">
-        <f>-H12-H13-H14</f>
+        <f>IF(0.003225*H8&gt;21.5,21.5,0.003225*H8)</f>
         <v/>
       </c>
       <c r="I15" s="730" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="163" t="inlineStr">
+      <c r="B16" s="101" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="C16" s="102" t="inlineStr">
+        <is>
+          <t>EEEEEEEE</t>
+        </is>
+      </c>
+      <c r="D16" s="102" t="inlineStr">
+        <is>
+          <t>Elkanah's Wallet Suspense Account</t>
+        </is>
+      </c>
+      <c r="E16" s="102" t="inlineStr">
+        <is>
+          <t>Part Fees (Revenue to 9PSB + VAT)</t>
+        </is>
+      </c>
+      <c r="F16" s="729" t="inlineStr">
+        <is>
+          <t>IF (Silver Agent = 0.001375 * Nxxx capped at N70.50), 
+IF (Gold Agent = 0.000875 * Nxxx capped at N60.50), 
+IF (Platinum Agent = 0.000375 * Nxxx capped at N50.50)</t>
+        </is>
+      </c>
+      <c r="G16" s="797" t="n"/>
+      <c r="H16" s="798">
+        <f>-H12-H13-H14-H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="731" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="163" t="inlineStr">
         <is>
           <t>Note: SLPSLPSLP is a varying SLP commission wallets on Elkanah. This is the wallet of the SLP which the transacting Agent's Main Wallet is mapped to. Where an Agent has no SLP the commission is credited to the Bank</t>
         </is>
       </c>
-      <c r="I16" s="731" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="163" t="n"/>
       <c r="I17" s="731" t="n"/>
     </row>
     <row r="18">
@@ -6029,32 +6060,61 @@
       </c>
       <c r="E17" s="102" t="inlineStr">
         <is>
-          <t>Part Fees</t>
+          <t>ISW Fee (pass-through; settled at switch on Core Banking)</t>
         </is>
       </c>
       <c r="F17" s="729" t="inlineStr">
         <is>
-          <t>IF (Silver Agent = 0.0046 * Nxxx capped at N92.00), 
-IF (Gold Agent = 0.0041 * Nxxx capped at N82.00), 
-IF (Platinum Agent = 0.0036 * Nxxx capped at N72.00)</t>
+          <t>0.003225 * Nxxx (capped at N21.50)</t>
         </is>
       </c>
       <c r="H17" s="796">
-        <f>-H14-H15-H16</f>
+        <f>IF(0.003225*H10&gt;21.5,21.5,0.003225*H10)</f>
         <v/>
       </c>
       <c r="I17" s="730" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="163" t="inlineStr">
+      <c r="B18" s="101" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="C18" s="102" t="inlineStr">
+        <is>
+          <t>EEEEEEEE</t>
+        </is>
+      </c>
+      <c r="D18" s="102" t="inlineStr">
+        <is>
+          <t>Elkanah's Wallet Suspense Account</t>
+        </is>
+      </c>
+      <c r="E18" s="102" t="inlineStr">
+        <is>
+          <t>Part Fees (Revenue to 9PSB + VAT)</t>
+        </is>
+      </c>
+      <c r="F18" s="729" t="inlineStr">
+        <is>
+          <t>IF (Silver Agent = 0.001375 * Nxxx capped at N70.50), 
+IF (Gold Agent = 0.000875 * Nxxx capped at N60.50), 
+IF (Platinum Agent = 0.000375 * Nxxx capped at N50.50)</t>
+        </is>
+      </c>
+      <c r="G18" s="797" t="n"/>
+      <c r="H18" s="798">
+        <f>-H14-H15-H16-H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="731" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="163" t="inlineStr">
         <is>
           <t>Note: SLPSLPSLP is a varying SLP commission wallets on Elkanah. This is the wallet of the SLP which the transacting Agent's Main Wallet is mapped to. Where an Agent has no SLP the commission is credited to the Bank</t>
         </is>
       </c>
-      <c r="I18" s="731" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="163" t="n"/>
       <c r="I19" s="731" t="n"/>
     </row>
     <row r="20">
